--- a/out/final/car_summary.xlsx
+++ b/out/final/car_summary.xlsx
@@ -597,46 +597,46 @@
         <v>28</v>
       </c>
       <c r="E3">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F3">
-        <v>0.01151580024990956</v>
+        <v>0.011846679371183</v>
       </c>
       <c r="G3">
-        <v>0.01749065453227544</v>
+        <v>0.01826041596976902</v>
       </c>
       <c r="H3">
-        <v>0.1038817836245635</v>
+        <v>0.1042410300849103</v>
       </c>
       <c r="I3">
-        <v>1.234427442498294</v>
+        <v>1.260406098623651</v>
       </c>
       <c r="J3">
-        <v>0.2193968550434158</v>
+        <v>0.2099282749780187</v>
       </c>
       <c r="K3">
-        <v>3032</v>
+        <v>2963</v>
       </c>
       <c r="L3">
-        <v>0.03553716727833377</v>
+        <v>0.03191791631561806</v>
       </c>
       <c r="M3">
-        <v>0.02437017012239948</v>
+        <v>0.01869342540925406</v>
       </c>
       <c r="N3">
-        <v>0.6048387096774194</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="O3">
         <v>-0.6151578735743707</v>
       </c>
       <c r="P3">
-        <v>-0.03648643484885525</v>
+        <v>-0.03654090056664977</v>
       </c>
       <c r="Q3">
-        <v>0.01749065453227544</v>
+        <v>0.01826041596976902</v>
       </c>
       <c r="R3">
-        <v>0.06456331767256759</v>
+        <v>0.06483036824006777</v>
       </c>
       <c r="S3">
         <v>0.2435279385701472</v>
@@ -774,46 +774,46 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="F6">
-        <v>0.01959960994508421</v>
+        <v>0.01453023091000428</v>
       </c>
       <c r="G6">
-        <v>0.03087134971765326</v>
+        <v>0.02981243299090408</v>
       </c>
       <c r="H6">
-        <v>0.1527748691228567</v>
+        <v>0.1564309012528873</v>
       </c>
       <c r="I6">
-        <v>1.428585871539553</v>
+        <v>0.9873910591127448</v>
       </c>
       <c r="J6">
-        <v>0.1556577910200216</v>
+        <v>0.3255792808740701</v>
       </c>
       <c r="K6">
-        <v>2874</v>
+        <v>2533</v>
       </c>
       <c r="L6">
-        <v>0.01255362058129347</v>
+        <v>0.04888437639545334</v>
       </c>
       <c r="M6">
-        <v>0.008933408183144214</v>
+        <v>0.02353400212601001</v>
       </c>
       <c r="N6">
-        <v>0.6209677419354839</v>
+        <v>0.6106194690265486</v>
       </c>
       <c r="O6">
         <v>-0.6596764095334604</v>
       </c>
       <c r="P6">
-        <v>-0.05137048168676198</v>
+        <v>-0.05411590779855757</v>
       </c>
       <c r="Q6">
-        <v>0.03087134971765326</v>
+        <v>0.02981243299090408</v>
       </c>
       <c r="R6">
-        <v>0.1116988605193038</v>
+        <v>0.1107955482953951</v>
       </c>
       <c r="S6">
         <v>0.4111727541048272</v>
@@ -1305,46 +1305,46 @@
         <v>28</v>
       </c>
       <c r="E15">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F15">
-        <v>0.006241767964342147</v>
+        <v>0.00655069494906158</v>
       </c>
       <c r="G15">
-        <v>0.01209191355057658</v>
+        <v>0.01227505802002051</v>
       </c>
       <c r="H15">
-        <v>0.1083372713318079</v>
+        <v>0.1087255164888246</v>
       </c>
       <c r="I15">
-        <v>0.6415648613943791</v>
+        <v>0.6682030476478505</v>
       </c>
       <c r="J15">
-        <v>0.5223495153059352</v>
+        <v>0.5052662094233906</v>
       </c>
       <c r="K15">
-        <v>3220</v>
+        <v>3146</v>
       </c>
       <c r="L15">
-        <v>0.1023913118829477</v>
+        <v>0.09227116277902724</v>
       </c>
       <c r="M15">
-        <v>0.1265100563218553</v>
+        <v>0.104203866405326</v>
       </c>
       <c r="N15">
-        <v>0.5725806451612904</v>
+        <v>0.5772357723577236</v>
       </c>
       <c r="O15">
         <v>-0.7062499396401718</v>
       </c>
       <c r="P15">
-        <v>-0.03964105262416984</v>
+        <v>-0.03982689801495964</v>
       </c>
       <c r="Q15">
-        <v>0.01209191355057658</v>
+        <v>0.01227505802002051</v>
       </c>
       <c r="R15">
-        <v>0.05972039529923064</v>
+        <v>0.06078985363324877</v>
       </c>
       <c r="S15">
         <v>0.23121546078401</v>
@@ -1482,46 +1482,46 @@
         <v>31</v>
       </c>
       <c r="E18">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="F18">
-        <v>0.008421452318361796</v>
+        <v>0.003138137240721788</v>
       </c>
       <c r="G18">
-        <v>0.02411083778016018</v>
+        <v>0.01964699738379661</v>
       </c>
       <c r="H18">
-        <v>0.1640435629136172</v>
+        <v>0.1685281231336839</v>
       </c>
       <c r="I18">
-        <v>0.5716611035342841</v>
+        <v>0.1979423720442414</v>
       </c>
       <c r="J18">
-        <v>0.5685947870115527</v>
+        <v>0.8434489746478218</v>
       </c>
       <c r="K18">
-        <v>3096</v>
+        <v>2705</v>
       </c>
       <c r="L18">
-        <v>0.05206601610488708</v>
+        <v>0.1397182781603141</v>
       </c>
       <c r="M18">
-        <v>0.0588758732807349</v>
+        <v>0.1319242908242605</v>
       </c>
       <c r="N18">
-        <v>0.5887096774193549</v>
+        <v>0.5752212389380531</v>
       </c>
       <c r="O18">
         <v>-0.7990409176250628</v>
       </c>
       <c r="P18">
-        <v>-0.0597494993096539</v>
+        <v>-0.06139493896840495</v>
       </c>
       <c r="Q18">
-        <v>0.02411083778016018</v>
+        <v>0.01964699738379661</v>
       </c>
       <c r="R18">
-        <v>0.101684976887558</v>
+        <v>0.101516322217895</v>
       </c>
       <c r="S18">
         <v>0.3881814630189198</v>
@@ -1954,49 +1954,49 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F26">
-        <v>0.004913237150832938</v>
+        <v>-0.001647178464683089</v>
       </c>
       <c r="G26">
-        <v>0.005076915315977371</v>
+        <v>0.001192850266152401</v>
       </c>
       <c r="H26">
-        <v>0.0608551229058672</v>
+        <v>0.06113122157344007</v>
       </c>
       <c r="I26">
-        <v>0.9062663519794059</v>
+        <v>-0.300046402438265</v>
       </c>
       <c r="J26">
-        <v>0.3665385206194967</v>
+        <v>0.7646482551331553</v>
       </c>
       <c r="K26">
-        <v>3206</v>
+        <v>3800</v>
       </c>
       <c r="L26">
-        <v>0.05305495675304553</v>
+        <v>0.8516400592835778</v>
       </c>
       <c r="M26">
-        <v>0.3271229672167791</v>
+        <v>0.7877465824023323</v>
       </c>
       <c r="N26">
-        <v>0.5476190476190477</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="O26">
         <v>-0.4710984164434994</v>
       </c>
       <c r="P26">
-        <v>-0.01659062416401938</v>
+        <v>-0.02291413013343804</v>
       </c>
       <c r="Q26">
-        <v>0.005076915315977371</v>
+        <v>0.001192850266152401</v>
       </c>
       <c r="R26">
-        <v>0.04117926416429349</v>
+        <v>0.02682846318332827</v>
       </c>
       <c r="S26">
-        <v>0.09207722853921407</v>
+        <v>0.1446052158261278</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -2013,46 +2013,46 @@
         <v>28</v>
       </c>
       <c r="E27">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F27">
-        <v>0.01424551384330303</v>
+        <v>0.006708564240445972</v>
       </c>
       <c r="G27">
-        <v>0.03286163408263565</v>
+        <v>0.02280284036827662</v>
       </c>
       <c r="H27">
-        <v>0.1060186311725901</v>
+        <v>0.1116811888899429</v>
       </c>
       <c r="I27">
-        <v>1.508277314392429</v>
+        <v>0.6661961370018944</v>
       </c>
       <c r="J27">
-        <v>0.1340069298675477</v>
+        <v>0.5065435270797732</v>
       </c>
       <c r="K27">
-        <v>2872</v>
+        <v>3172</v>
       </c>
       <c r="L27">
-        <v>0.006001362341114421</v>
+        <v>0.1056830976755944</v>
       </c>
       <c r="M27">
-        <v>0.005536025163897815</v>
+        <v>0.07090166737501427</v>
       </c>
       <c r="N27">
-        <v>0.626984126984127</v>
+        <v>0.5853658536585366</v>
       </c>
       <c r="O27">
         <v>-0.6151578735743707</v>
       </c>
       <c r="P27">
-        <v>-0.02859451745018227</v>
+        <v>-0.04283554106527321</v>
       </c>
       <c r="Q27">
-        <v>0.03286163408263565</v>
+        <v>0.02280284036827662</v>
       </c>
       <c r="R27">
-        <v>0.07254434527079834</v>
+        <v>0.07188164379608386</v>
       </c>
       <c r="S27">
         <v>0.3051966849554455</v>
@@ -2072,46 +2072,46 @@
         <v>29</v>
       </c>
       <c r="E28">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F28">
-        <v>-0.001440157067084521</v>
+        <v>-0.001521740141105669</v>
       </c>
       <c r="G28">
-        <v>0.0006327093043352328</v>
+        <v>0.001086873335108707</v>
       </c>
       <c r="H28">
-        <v>0.04063495841895332</v>
+        <v>0.03957239643563187</v>
       </c>
       <c r="I28">
-        <v>-0.3978279691551084</v>
+        <v>-0.4282121524238586</v>
       </c>
       <c r="J28">
-        <v>0.6914355904355908</v>
+        <v>0.6692455585587206</v>
       </c>
       <c r="K28">
-        <v>3830</v>
+        <v>3833</v>
       </c>
       <c r="L28">
-        <v>0.678040363574274</v>
+        <v>0.9165863311402348</v>
       </c>
       <c r="M28">
-        <v>1</v>
+        <v>0.7877465824023323</v>
       </c>
       <c r="N28">
-        <v>0.5</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="O28">
-        <v>-0.104449111287138</v>
+        <v>-0.1641781035903104</v>
       </c>
       <c r="P28">
-        <v>-0.01992803157325626</v>
+        <v>-0.02117889197223996</v>
       </c>
       <c r="Q28">
-        <v>0.0006327093043352328</v>
+        <v>0.001086873335108707</v>
       </c>
       <c r="R28">
-        <v>0.02130740091805133</v>
+        <v>0.01923142064753205</v>
       </c>
       <c r="S28">
         <v>0.08239107533804257</v>
@@ -2131,49 +2131,49 @@
         <v>30</v>
       </c>
       <c r="E29">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F29">
-        <v>0.006441651396472662</v>
+        <v>-0.0007530199972306806</v>
       </c>
       <c r="G29">
-        <v>0.01162739336764174</v>
+        <v>0.002773970658942526</v>
       </c>
       <c r="H29">
-        <v>0.08330262424667986</v>
+        <v>0.08037013886107021</v>
       </c>
       <c r="I29">
-        <v>0.8645568215963744</v>
+        <v>-0.1043332253618932</v>
       </c>
       <c r="J29">
-        <v>0.3889514903303488</v>
+        <v>0.9170748481829025</v>
       </c>
       <c r="K29">
-        <v>3352</v>
+        <v>3689</v>
       </c>
       <c r="L29">
-        <v>0.1491141507915992</v>
+        <v>0.6427730762903969</v>
       </c>
       <c r="M29">
-        <v>0.4744215734409516</v>
+        <v>0.9284921641248497</v>
       </c>
       <c r="N29">
-        <v>0.536</v>
+        <v>0.5080645161290323</v>
       </c>
       <c r="O29">
         <v>-0.4716777713227482</v>
       </c>
       <c r="P29">
-        <v>-0.03884780431358903</v>
+        <v>-0.04082698015564165</v>
       </c>
       <c r="Q29">
-        <v>0.01162739336764174</v>
+        <v>0.002773970658942526</v>
       </c>
       <c r="R29">
-        <v>0.05708295715751976</v>
+        <v>0.04866399268370689</v>
       </c>
       <c r="S29">
-        <v>0.1476564177113768</v>
+        <v>0.13686617922487</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -2190,46 +2190,46 @@
         <v>31</v>
       </c>
       <c r="E30">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="F30">
-        <v>0.02802617460159368</v>
+        <v>0.02157332801105191</v>
       </c>
       <c r="G30">
-        <v>0.04283899168262939</v>
+        <v>0.02875506432362873</v>
       </c>
       <c r="H30">
-        <v>0.1290739034655434</v>
+        <v>0.1316295173107571</v>
       </c>
       <c r="I30">
-        <v>2.427618204603653</v>
+        <v>1.772787941080474</v>
       </c>
       <c r="J30">
-        <v>0.01663489666209544</v>
+        <v>0.07888867379461235</v>
       </c>
       <c r="K30">
-        <v>2668</v>
+        <v>2571</v>
       </c>
       <c r="L30">
-        <v>0.001759772462700567</v>
+        <v>0.01662961545289519</v>
       </c>
       <c r="M30">
-        <v>0.0001501334225702843</v>
+        <v>0.01586449682440639</v>
       </c>
       <c r="N30">
-        <v>0.672</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="O30">
         <v>-0.6008766263938626</v>
       </c>
       <c r="P30">
-        <v>-0.041292085059767</v>
+        <v>-0.04092888223349755</v>
       </c>
       <c r="Q30">
-        <v>0.04283899168262939</v>
+        <v>0.02875506432362873</v>
       </c>
       <c r="R30">
-        <v>0.1066721232662955</v>
+        <v>0.1084904019670709</v>
       </c>
       <c r="S30">
         <v>0.3268837448716404</v>
@@ -2249,46 +2249,46 @@
         <v>32</v>
       </c>
       <c r="E31">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F31">
-        <v>0.006711203751559401</v>
+        <v>0.003472405331445724</v>
       </c>
       <c r="G31">
-        <v>-0.001740352233788767</v>
+        <v>0.004596198034364563</v>
       </c>
       <c r="H31">
-        <v>0.09452165159990414</v>
+        <v>0.09749053535125173</v>
       </c>
       <c r="I31">
-        <v>0.7938238247708344</v>
+        <v>0.3966238279042591</v>
       </c>
       <c r="J31">
-        <v>0.4288144919920555</v>
+        <v>0.6923321654212456</v>
       </c>
       <c r="K31">
-        <v>3662</v>
+        <v>3704</v>
       </c>
       <c r="L31">
-        <v>0.4972456490178682</v>
+        <v>0.669801956146495</v>
       </c>
       <c r="M31">
-        <v>1</v>
+        <v>0.9284921641248497</v>
       </c>
       <c r="N31">
-        <v>0.496</v>
+        <v>0.5080645161290323</v>
       </c>
       <c r="O31">
         <v>-0.3810893221196768</v>
       </c>
       <c r="P31">
-        <v>-0.05032182665256679</v>
+        <v>-0.05062724334712859</v>
       </c>
       <c r="Q31">
-        <v>-0.001740352233788767</v>
+        <v>0.004596198034364563</v>
       </c>
       <c r="R31">
-        <v>0.06170078073080409</v>
+        <v>0.05655443261192933</v>
       </c>
       <c r="S31">
         <v>0.297451644799397</v>
@@ -2308,46 +2308,46 @@
         <v>33</v>
       </c>
       <c r="E32">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F32">
-        <v>-0.001275812179351532</v>
+        <v>0.003078332807382322</v>
       </c>
       <c r="G32">
-        <v>0.006022233712789427</v>
+        <v>0.006069789060602293</v>
       </c>
       <c r="H32">
-        <v>0.06380211812530646</v>
+        <v>0.05816848737521108</v>
       </c>
       <c r="I32">
-        <v>-0.2244589461261193</v>
+        <v>0.58930298776096</v>
       </c>
       <c r="J32">
-        <v>0.8227666954595833</v>
+        <v>0.5567388799256435</v>
       </c>
       <c r="K32">
-        <v>3810</v>
+        <v>3573</v>
       </c>
       <c r="L32">
-        <v>0.6427657272712657</v>
+        <v>0.4513944349812031</v>
       </c>
       <c r="M32">
-        <v>0.4227911341458804</v>
+        <v>0.5297694043652676</v>
       </c>
       <c r="N32">
-        <v>0.5396825396825397</v>
+        <v>0.532258064516129</v>
       </c>
       <c r="O32">
-        <v>-0.2596941469973632</v>
+        <v>-0.1539596832972503</v>
       </c>
       <c r="P32">
-        <v>-0.03981115931081314</v>
+        <v>-0.02933116236043898</v>
       </c>
       <c r="Q32">
-        <v>0.006022233712789427</v>
+        <v>0.006069789060602293</v>
       </c>
       <c r="R32">
-        <v>0.03756499022782084</v>
+        <v>0.04138451560388978</v>
       </c>
       <c r="S32">
         <v>0.1285087530406699</v>
@@ -2367,46 +2367,46 @@
         <v>34</v>
       </c>
       <c r="E33">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F33">
-        <v>0.006293290298741697</v>
+        <v>0.004112622222149855</v>
       </c>
       <c r="G33">
-        <v>0.005417411898480329</v>
+        <v>0.007406416270267779</v>
       </c>
       <c r="H33">
-        <v>0.04965757547862763</v>
+        <v>0.04979857470730974</v>
       </c>
       <c r="I33">
-        <v>1.42258271208998</v>
+        <v>0.9196291894236743</v>
       </c>
       <c r="J33">
-        <v>0.1573478989378541</v>
+        <v>0.3595665768480693</v>
       </c>
       <c r="K33">
-        <v>3471</v>
+        <v>3428</v>
       </c>
       <c r="L33">
-        <v>0.1973135894286239</v>
+        <v>0.2649891215367504</v>
       </c>
       <c r="M33">
-        <v>0.4227911341458804</v>
+        <v>0.1265100563218553</v>
       </c>
       <c r="N33">
-        <v>0.5396825396825397</v>
+        <v>0.5725806451612904</v>
       </c>
       <c r="O33">
-        <v>-0.1395201595370045</v>
+        <v>-0.1391355028831285</v>
       </c>
       <c r="P33">
-        <v>-0.01618223257434559</v>
+        <v>-0.02155310144559014</v>
       </c>
       <c r="Q33">
-        <v>0.005417411898480329</v>
+        <v>0.007406416270267779</v>
       </c>
       <c r="R33">
-        <v>0.02594241241136219</v>
+        <v>0.02824762665393107</v>
       </c>
       <c r="S33">
         <v>0.1906491164796925</v>
@@ -2426,49 +2426,49 @@
         <v>35</v>
       </c>
       <c r="E34">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F34">
-        <v>0.01113217279169253</v>
+        <v>0.01076794548160344</v>
       </c>
       <c r="G34">
-        <v>0.01361053099084081</v>
+        <v>0.01049140121263298</v>
       </c>
       <c r="H34">
-        <v>0.06123262896050644</v>
+        <v>0.06138061594488849</v>
       </c>
       <c r="I34">
-        <v>2.040714759303179</v>
+        <v>1.953495649740572</v>
       </c>
       <c r="J34">
-        <v>0.04338497129970329</v>
+        <v>0.05303118727037582</v>
       </c>
       <c r="K34">
-        <v>3268</v>
+        <v>3017</v>
       </c>
       <c r="L34">
-        <v>0.07450270195839315</v>
+        <v>0.03238870921171225</v>
       </c>
       <c r="M34">
-        <v>0.06093825261566016</v>
+        <v>0.0588758732807349</v>
       </c>
       <c r="N34">
-        <v>0.5873015873015873</v>
+        <v>0.5887096774193549</v>
       </c>
       <c r="O34">
-        <v>-0.1212933711424545</v>
+        <v>-0.1602402713514575</v>
       </c>
       <c r="P34">
-        <v>-0.03655730689081713</v>
+        <v>-0.02929123781457482</v>
       </c>
       <c r="Q34">
-        <v>0.01361053099084081</v>
+        <v>0.01049140121263298</v>
       </c>
       <c r="R34">
-        <v>0.05148064228599952</v>
+        <v>0.05177454922251312</v>
       </c>
       <c r="S34">
-        <v>0.136989278022573</v>
+        <v>0.1328974238733034</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -2485,49 +2485,49 @@
         <v>36</v>
       </c>
       <c r="E35">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F35">
-        <v>-0.005071475278376844</v>
+        <v>-0.002366800101149718</v>
       </c>
       <c r="G35">
-        <v>0.0001666784431317847</v>
+        <v>0.0004534339472558324</v>
       </c>
       <c r="H35">
-        <v>0.03110153571378085</v>
+        <v>0.03255642500532013</v>
       </c>
       <c r="I35">
-        <v>-1.830365205609974</v>
+        <v>-0.8095351535047522</v>
       </c>
       <c r="J35">
-        <v>0.06957756818309421</v>
+        <v>0.4197706827375777</v>
       </c>
       <c r="K35">
-        <v>3705</v>
+        <v>3704</v>
       </c>
       <c r="L35">
-        <v>0.4718374589059187</v>
+        <v>0.669801956146495</v>
       </c>
       <c r="M35">
-        <v>0.9290596866317961</v>
+        <v>0.7877465824023323</v>
       </c>
       <c r="N35">
-        <v>0.5079365079365079</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="O35">
-        <v>-0.08839193461339623</v>
+        <v>-0.1392728518307003</v>
       </c>
       <c r="P35">
-        <v>-0.01570313169230553</v>
+        <v>-0.01557463188003827</v>
       </c>
       <c r="Q35">
-        <v>0.0001666784431317847</v>
+        <v>0.0004534339472558324</v>
       </c>
       <c r="R35">
-        <v>0.01680736764973989</v>
+        <v>0.01194305137901588</v>
       </c>
       <c r="S35">
-        <v>0.0703273210946509</v>
+        <v>0.09744494703969608</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -2544,49 +2544,49 @@
         <v>37</v>
       </c>
       <c r="E36">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F36">
-        <v>-0.005316255121843781</v>
+        <v>0.002026827195601676</v>
       </c>
       <c r="G36">
-        <v>-0.002699282127191227</v>
+        <v>0.003614655807093248</v>
       </c>
       <c r="H36">
-        <v>0.04445751403069972</v>
+        <v>0.04460725478822427</v>
       </c>
       <c r="I36">
-        <v>-1.342288633112883</v>
+        <v>0.5059668559682267</v>
       </c>
       <c r="J36">
-        <v>0.1819352503580759</v>
+        <v>0.6137855334210134</v>
       </c>
       <c r="K36">
-        <v>3687</v>
+        <v>3638</v>
       </c>
       <c r="L36">
-        <v>0.4452728381954807</v>
+        <v>0.5545184652607543</v>
       </c>
       <c r="M36">
-        <v>0.7893959446881439</v>
+        <v>0.3232476471849839</v>
       </c>
       <c r="N36">
-        <v>0.4841269841269841</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="O36">
-        <v>-0.2265968199888795</v>
+        <v>-0.1101247554184753</v>
       </c>
       <c r="P36">
-        <v>-0.03146135434877073</v>
+        <v>-0.02549269245060712</v>
       </c>
       <c r="Q36">
-        <v>-0.002699282127191227</v>
+        <v>0.003614655807093248</v>
       </c>
       <c r="R36">
-        <v>0.02272346844321674</v>
+        <v>0.03026763322730511</v>
       </c>
       <c r="S36">
-        <v>0.06562873244499468</v>
+        <v>0.1498206032170635</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -2603,49 +2603,49 @@
         <v>38</v>
       </c>
       <c r="E37">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F37">
-        <v>0.004838882492950836</v>
+        <v>0.00665532325945359</v>
       </c>
       <c r="G37">
-        <v>0.009381557661471585</v>
+        <v>0.008298924930034091</v>
       </c>
       <c r="H37">
-        <v>0.04880083938951085</v>
+        <v>0.05618052125865079</v>
       </c>
       <c r="I37">
-        <v>1.11302022567498</v>
+        <v>1.319150155140065</v>
       </c>
       <c r="J37">
-        <v>0.267835559871506</v>
+        <v>0.1895694166439328</v>
       </c>
       <c r="K37">
-        <v>3503</v>
+        <v>3307</v>
       </c>
       <c r="L37">
-        <v>0.2257695331003672</v>
+        <v>0.1566548953943388</v>
       </c>
       <c r="M37">
-        <v>0.01581820400805213</v>
+        <v>0.02437017012239948</v>
       </c>
       <c r="N37">
-        <v>0.6111111111111112</v>
+        <v>0.6048387096774194</v>
       </c>
       <c r="O37">
         <v>-0.1277418931541138</v>
       </c>
       <c r="P37">
-        <v>-0.027357589469307</v>
+        <v>-0.02856812776015152</v>
       </c>
       <c r="Q37">
-        <v>0.009381557661471585</v>
+        <v>0.008298924930034091</v>
       </c>
       <c r="R37">
-        <v>0.03242195276584961</v>
+        <v>0.0371319064615849</v>
       </c>
       <c r="S37">
-        <v>0.1247141333426937</v>
+        <v>0.138151985855692</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -2662,49 +2662,49 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F38">
-        <v>0.003290883110008803</v>
+        <v>-0.003537075385228132</v>
       </c>
       <c r="G38">
-        <v>0.004810981938247949</v>
+        <v>0.0001872308578329852</v>
       </c>
       <c r="H38">
-        <v>0.06538825148411376</v>
+        <v>0.06605973491608201</v>
       </c>
       <c r="I38">
-        <v>0.5649343797134077</v>
+        <v>-0.5962361884598518</v>
       </c>
       <c r="J38">
-        <v>0.5731308732015917</v>
+        <v>0.5521131569313475</v>
       </c>
       <c r="K38">
-        <v>3287</v>
+        <v>3862</v>
       </c>
       <c r="L38">
-        <v>0.0823426967420248</v>
+        <v>0.9741388025092916</v>
       </c>
       <c r="M38">
-        <v>0.3271229672167791</v>
+        <v>0.9284921641248497</v>
       </c>
       <c r="N38">
-        <v>0.5476190476190477</v>
+        <v>0.5080645161290323</v>
       </c>
       <c r="O38">
         <v>-0.5431406332680223</v>
       </c>
       <c r="P38">
-        <v>-0.0172803625076538</v>
+        <v>-0.02343404408896441</v>
       </c>
       <c r="Q38">
-        <v>0.004810981938247949</v>
+        <v>0.0001872308578329852</v>
       </c>
       <c r="R38">
-        <v>0.0404546286296972</v>
+        <v>0.02225528430535684</v>
       </c>
       <c r="S38">
-        <v>0.0892610967236452</v>
+        <v>0.1404246404947259</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -2721,46 +2721,46 @@
         <v>28</v>
       </c>
       <c r="E39">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F39">
-        <v>0.008767376769332799</v>
+        <v>0.001031925172357973</v>
       </c>
       <c r="G39">
-        <v>0.03047549399703362</v>
+        <v>0.01949474818299934</v>
       </c>
       <c r="H39">
-        <v>0.111240979399953</v>
+        <v>0.1172557310484154</v>
       </c>
       <c r="I39">
-        <v>0.8846880051368416</v>
+        <v>0.09760379039548521</v>
       </c>
       <c r="J39">
-        <v>0.3780234883632879</v>
+        <v>0.922407085391908</v>
       </c>
       <c r="K39">
-        <v>3061</v>
+        <v>3339</v>
       </c>
       <c r="L39">
-        <v>0.02216526461482268</v>
+        <v>0.231543839121331</v>
       </c>
       <c r="M39">
-        <v>0.009503165032902208</v>
+        <v>0.07090166737501427</v>
       </c>
       <c r="N39">
-        <v>0.6190476190476191</v>
+        <v>0.5853658536585366</v>
       </c>
       <c r="O39">
         <v>-0.7062499396401718</v>
       </c>
       <c r="P39">
-        <v>-0.03430951075230029</v>
+        <v>-0.04812958569048796</v>
       </c>
       <c r="Q39">
-        <v>0.03047549399703362</v>
+        <v>0.01949474818299934</v>
       </c>
       <c r="R39">
-        <v>0.06918738143878847</v>
+        <v>0.06851782290002735</v>
       </c>
       <c r="S39">
         <v>0.2928243202433803</v>
@@ -2780,46 +2780,46 @@
         <v>29</v>
       </c>
       <c r="E40">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F40">
-        <v>-0.00218109618825017</v>
+        <v>-0.002315571894896554</v>
       </c>
       <c r="G40">
-        <v>-0.0003207624414244142</v>
+        <v>0.0001125079120473235</v>
       </c>
       <c r="H40">
-        <v>0.04098292232441112</v>
+        <v>0.04011348092396178</v>
       </c>
       <c r="I40">
-        <v>-0.5973889269850646</v>
+        <v>-0.6428042831991899</v>
       </c>
       <c r="J40">
-        <v>0.5513283770950612</v>
+        <v>0.5215475645938598</v>
       </c>
       <c r="K40">
-        <v>3902</v>
+        <v>3863</v>
       </c>
       <c r="L40">
-        <v>0.8104613765540828</v>
+        <v>0.9761275069396042</v>
       </c>
       <c r="M40">
-        <v>1</v>
+        <v>0.7877465824023323</v>
       </c>
       <c r="N40">
-        <v>0.5</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="O40">
-        <v>-0.1069841967739239</v>
+        <v>-0.1772451296261738</v>
       </c>
       <c r="P40">
-        <v>-0.0200758991901924</v>
+        <v>-0.0219695200307295</v>
       </c>
       <c r="Q40">
-        <v>-0.0003207624414244142</v>
+        <v>0.0001125079120473235</v>
       </c>
       <c r="R40">
-        <v>0.02118131533650788</v>
+        <v>0.01913773365466347</v>
       </c>
       <c r="S40">
         <v>0.08045238347673758</v>
@@ -2839,49 +2839,49 @@
         <v>30</v>
       </c>
       <c r="E41">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F41">
-        <v>0.002830154141625771</v>
+        <v>-0.00482423745853047</v>
       </c>
       <c r="G41">
-        <v>0.009385334025000573</v>
+        <v>-0.0005201222125477247</v>
       </c>
       <c r="H41">
-        <v>0.08784254913504767</v>
+        <v>0.08546324693499818</v>
       </c>
       <c r="I41">
-        <v>0.3602136498650892</v>
+        <v>-0.6285793803239194</v>
       </c>
       <c r="J41">
-        <v>0.7193001932105302</v>
+        <v>0.5307899910202011</v>
       </c>
       <c r="K41">
-        <v>3515</v>
+        <v>3871</v>
       </c>
       <c r="L41">
-        <v>0.297858481863961</v>
+        <v>0.9920414466684371</v>
       </c>
       <c r="M41">
-        <v>0.5916839270941637</v>
+        <v>1</v>
       </c>
       <c r="N41">
-        <v>0.528</v>
+        <v>0.5</v>
       </c>
       <c r="O41">
         <v>-0.5600934569199053</v>
       </c>
       <c r="P41">
-        <v>-0.04349074139756576</v>
+        <v>-0.04360318284385846</v>
       </c>
       <c r="Q41">
-        <v>0.009385334025000573</v>
+        <v>-0.0005201222125477247</v>
       </c>
       <c r="R41">
-        <v>0.05458481226550966</v>
+        <v>0.04785085177769956</v>
       </c>
       <c r="S41">
-        <v>0.1449673864131078</v>
+        <v>0.1323020047582137</v>
       </c>
     </row>
     <row r="42" spans="1:19">
@@ -2898,46 +2898,46 @@
         <v>31</v>
       </c>
       <c r="E42">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="F42">
-        <v>0.01807945497594952</v>
+        <v>0.01134672521257036</v>
       </c>
       <c r="G42">
-        <v>0.03985462457466678</v>
+        <v>0.02248817084313751</v>
       </c>
       <c r="H42">
-        <v>0.1372821778104216</v>
+        <v>0.1404098832904531</v>
       </c>
       <c r="I42">
-        <v>1.472401260205715</v>
+        <v>0.8741093989351132</v>
       </c>
       <c r="J42">
-        <v>0.1434462081711682</v>
+        <v>0.3838647670930379</v>
       </c>
       <c r="K42">
-        <v>2949</v>
+        <v>2830</v>
       </c>
       <c r="L42">
-        <v>0.01486479493390091</v>
+        <v>0.09095829414910434</v>
       </c>
       <c r="M42">
-        <v>0.01195901352323824</v>
+        <v>0.06399591064679504</v>
       </c>
       <c r="N42">
-        <v>0.616</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="O42">
         <v>-0.758055079046148</v>
       </c>
       <c r="P42">
-        <v>-0.04676122709650152</v>
+        <v>-0.04740580174051361</v>
       </c>
       <c r="Q42">
-        <v>0.03985462457466678</v>
+        <v>0.02248817084313751</v>
       </c>
       <c r="R42">
-        <v>0.1015169580466977</v>
+        <v>0.09787977436595499</v>
       </c>
       <c r="S42">
         <v>0.3182231058569503</v>
@@ -2957,46 +2957,46 @@
         <v>32</v>
       </c>
       <c r="E43">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F43">
-        <v>0.0003975248308761493</v>
+        <v>-0.002888882177624284</v>
       </c>
       <c r="G43">
-        <v>-0.008082108028451995</v>
+        <v>-0.003507343643814931</v>
       </c>
       <c r="H43">
-        <v>0.09777780722001854</v>
+        <v>0.1013944870177963</v>
       </c>
       <c r="I43">
-        <v>0.04545471870641366</v>
+        <v>-0.3172680430676312</v>
       </c>
       <c r="J43">
-        <v>0.9638179877934694</v>
+        <v>0.751578139720707</v>
       </c>
       <c r="K43">
-        <v>3927</v>
+        <v>3799</v>
       </c>
       <c r="L43">
-        <v>0.9793594973007338</v>
+        <v>0.8496853414823469</v>
       </c>
       <c r="M43">
-        <v>0.2830852395827475</v>
+        <v>0.9284921641248497</v>
       </c>
       <c r="N43">
-        <v>0.448</v>
+        <v>0.4919354838709677</v>
       </c>
       <c r="O43">
         <v>-0.4780812848584236</v>
       </c>
       <c r="P43">
-        <v>-0.05615722268417955</v>
+        <v>-0.05725549850471109</v>
       </c>
       <c r="Q43">
-        <v>-0.008082108028451995</v>
+        <v>-0.003507343643814931</v>
       </c>
       <c r="R43">
-        <v>0.05114034151438526</v>
+        <v>0.04942201966371815</v>
       </c>
       <c r="S43">
         <v>0.284662553500647</v>
@@ -3016,46 +3016,46 @@
         <v>33</v>
       </c>
       <c r="E44">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F44">
-        <v>-0.003101534770120065</v>
+        <v>0.001328072260167893</v>
       </c>
       <c r="G44">
-        <v>0.004831401385344403</v>
+        <v>0.005496029886763391</v>
       </c>
       <c r="H44">
-        <v>0.06473103081125149</v>
+        <v>0.05851722302766098</v>
       </c>
       <c r="I44">
-        <v>-0.5378354247189963</v>
+        <v>0.2527253693474347</v>
       </c>
       <c r="J44">
-        <v>0.5916469599093562</v>
+        <v>0.8009023094810096</v>
       </c>
       <c r="K44">
-        <v>3876</v>
+        <v>3675</v>
       </c>
       <c r="L44">
-        <v>0.7617858565792306</v>
+        <v>0.617964928490237</v>
       </c>
       <c r="M44">
-        <v>0.4227911341458804</v>
+        <v>0.6535984498230588</v>
       </c>
       <c r="N44">
-        <v>0.5396825396825397</v>
+        <v>0.5241935483870968</v>
       </c>
       <c r="O44">
-        <v>-0.2748578097155542</v>
+        <v>-0.1584532786002754</v>
       </c>
       <c r="P44">
-        <v>-0.04089656078427625</v>
+        <v>-0.03020027666639792</v>
       </c>
       <c r="Q44">
-        <v>0.004831401385344403</v>
+        <v>0.005496029886763391</v>
       </c>
       <c r="R44">
-        <v>0.0363339667763817</v>
+        <v>0.04010486061432487</v>
       </c>
       <c r="S44">
         <v>0.1252577752737178</v>
@@ -3075,46 +3075,46 @@
         <v>34</v>
       </c>
       <c r="E45">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F45">
-        <v>0.005078708265582275</v>
+        <v>0.003013537777935688</v>
       </c>
       <c r="G45">
-        <v>0.004917756321316178</v>
+        <v>0.00734251453185672</v>
       </c>
       <c r="H45">
-        <v>0.04956960720505942</v>
+        <v>0.04965198270771286</v>
       </c>
       <c r="I45">
-        <v>1.150066787007719</v>
+        <v>0.6758508857462372</v>
       </c>
       <c r="J45">
-        <v>0.2523118750215136</v>
+        <v>0.5004040707723816</v>
       </c>
       <c r="K45">
-        <v>3555</v>
+        <v>3516</v>
       </c>
       <c r="L45">
-        <v>0.2780468952281793</v>
+        <v>0.3706629380096301</v>
       </c>
       <c r="M45">
-        <v>0.4227911341458804</v>
+        <v>0.1265100563218553</v>
       </c>
       <c r="N45">
-        <v>0.5396825396825397</v>
+        <v>0.5725806451612904</v>
       </c>
       <c r="O45">
-        <v>-0.1531212473279444</v>
+        <v>-0.1422504343897148</v>
       </c>
       <c r="P45">
-        <v>-0.01770354541687361</v>
+        <v>-0.0227997847353647</v>
       </c>
       <c r="Q45">
-        <v>0.004917756321316178</v>
+        <v>0.00734251453185672</v>
       </c>
       <c r="R45">
-        <v>0.02444824205247827</v>
+        <v>0.02758746559839249</v>
       </c>
       <c r="S45">
         <v>0.1819067956576758</v>
@@ -3134,49 +3134,49 @@
         <v>35</v>
       </c>
       <c r="E46">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F46">
-        <v>0.008376662067688605</v>
+        <v>0.008052136724830678</v>
       </c>
       <c r="G46">
-        <v>0.01318442605897937</v>
+        <v>0.008030498987183634</v>
       </c>
       <c r="H46">
-        <v>0.06210556988178442</v>
+        <v>0.06219339597310371</v>
       </c>
       <c r="I46">
-        <v>1.51399944779843</v>
+        <v>1.441709339060225</v>
       </c>
       <c r="J46">
-        <v>0.1325504323373667</v>
+        <v>0.1519256372408581</v>
       </c>
       <c r="K46">
-        <v>3409</v>
+        <v>3148</v>
       </c>
       <c r="L46">
-        <v>0.1498100823725345</v>
+        <v>0.06984606033077201</v>
       </c>
       <c r="M46">
-        <v>0.09012286584573247</v>
+        <v>0.1265100563218553</v>
       </c>
       <c r="N46">
-        <v>0.5793650793650794</v>
+        <v>0.5725806451612904</v>
       </c>
       <c r="O46">
-        <v>-0.1396034477129872</v>
+        <v>-0.1789770720711075</v>
       </c>
       <c r="P46">
-        <v>-0.03891748130368589</v>
+        <v>-0.03039854589756734</v>
       </c>
       <c r="Q46">
-        <v>0.01318442605897937</v>
+        <v>0.008030498987183634</v>
       </c>
       <c r="R46">
-        <v>0.05073832750196598</v>
+        <v>0.05095343252828598</v>
       </c>
       <c r="S46">
-        <v>0.1339653865033411</v>
+        <v>0.1289465146637057</v>
       </c>
     </row>
     <row r="47" spans="1:19">
@@ -3193,49 +3193,49 @@
         <v>36</v>
       </c>
       <c r="E47">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F47">
-        <v>-0.00556439192249543</v>
+        <v>-0.00294478496964696</v>
       </c>
       <c r="G47">
-        <v>-5.727850458797797E-05</v>
+        <v>0.0001463060800420549</v>
       </c>
       <c r="H47">
-        <v>0.03155567505719656</v>
+        <v>0.0330625058470263</v>
       </c>
       <c r="I47">
-        <v>-1.979363277949785</v>
+        <v>-0.9918104142534316</v>
       </c>
       <c r="J47">
-        <v>0.04997274298816837</v>
+        <v>0.3232371327964975</v>
       </c>
       <c r="K47">
-        <v>3666</v>
+        <v>3653</v>
       </c>
       <c r="L47">
-        <v>0.415386622813677</v>
+        <v>0.5798542204433836</v>
       </c>
       <c r="M47">
-        <v>1</v>
+        <v>0.9284921641248497</v>
       </c>
       <c r="N47">
-        <v>0.5</v>
+        <v>0.5080645161290323</v>
       </c>
       <c r="O47">
-        <v>-0.0910386141902457</v>
+        <v>-0.15202449460289</v>
       </c>
       <c r="P47">
-        <v>-0.01589406157017936</v>
+        <v>-0.01580735087652946</v>
       </c>
       <c r="Q47">
-        <v>-5.727850458797797E-05</v>
+        <v>0.0001463060800420549</v>
       </c>
       <c r="R47">
-        <v>0.01666236091815368</v>
+        <v>0.01166511758096007</v>
       </c>
       <c r="S47">
-        <v>0.06911907834015113</v>
+        <v>0.09439806820287816</v>
       </c>
     </row>
     <row r="48" spans="1:19">
@@ -3252,49 +3252,49 @@
         <v>37</v>
       </c>
       <c r="E48">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F48">
-        <v>-0.006285087759706817</v>
+        <v>0.001024963708781597</v>
       </c>
       <c r="G48">
-        <v>-0.002759558336745413</v>
+        <v>0.003402015312715232</v>
       </c>
       <c r="H48">
-        <v>0.0452344814595446</v>
+        <v>0.04479758670285242</v>
       </c>
       <c r="I48">
-        <v>-1.559649472073306</v>
+        <v>0.2547796357335871</v>
       </c>
       <c r="J48">
-        <v>0.1213710098563996</v>
+        <v>0.7993187955960963</v>
       </c>
       <c r="K48">
-        <v>3612</v>
+        <v>3701</v>
       </c>
       <c r="L48">
-        <v>0.3441833227080483</v>
+        <v>0.6643604228001543</v>
       </c>
       <c r="M48">
-        <v>0.7893959446881439</v>
+        <v>0.4190737425166349</v>
       </c>
       <c r="N48">
-        <v>0.4841269841269841</v>
+        <v>0.5403225806451613</v>
       </c>
       <c r="O48">
-        <v>-0.2364379652460606</v>
+        <v>-0.1123597225886289</v>
       </c>
       <c r="P48">
-        <v>-0.03185118922642802</v>
+        <v>-0.02656642627455946</v>
       </c>
       <c r="Q48">
-        <v>-0.002759558336745413</v>
+        <v>0.003402015312715232</v>
       </c>
       <c r="R48">
-        <v>0.02157949366079052</v>
+        <v>0.02980213833010049</v>
       </c>
       <c r="S48">
-        <v>0.06489894644332905</v>
+        <v>0.1443607945547317</v>
       </c>
     </row>
     <row r="49" spans="1:19">
@@ -3311,49 +3311,49 @@
         <v>38</v>
       </c>
       <c r="E49">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F49">
-        <v>0.003297953802106332</v>
+        <v>0.00503859894689499</v>
       </c>
       <c r="G49">
-        <v>0.006786881027027079</v>
+        <v>0.006388340592976864</v>
       </c>
       <c r="H49">
-        <v>0.049133066350677</v>
+        <v>0.05646075417543765</v>
       </c>
       <c r="I49">
-        <v>0.7534526616037469</v>
+        <v>0.993742717922076</v>
       </c>
       <c r="J49">
-        <v>0.4525947659617958</v>
+        <v>0.3222990717215606</v>
       </c>
       <c r="K49">
-        <v>3607</v>
+        <v>3399</v>
       </c>
       <c r="L49">
-        <v>0.3380092832108151</v>
+        <v>0.2352303011500346</v>
       </c>
       <c r="M49">
-        <v>0.1812240608814235</v>
+        <v>0.0588758732807349</v>
       </c>
       <c r="N49">
-        <v>0.5634920634920635</v>
+        <v>0.5887096774193549</v>
       </c>
       <c r="O49">
         <v>-0.1301061985549944</v>
       </c>
       <c r="P49">
-        <v>-0.02873214743067238</v>
+        <v>-0.0298992171839575</v>
       </c>
       <c r="Q49">
-        <v>0.006786881027027079</v>
+        <v>0.006388340592976864</v>
       </c>
       <c r="R49">
-        <v>0.03126909051225921</v>
+        <v>0.03640447253130684</v>
       </c>
       <c r="S49">
-        <v>0.1220709442170306</v>
+        <v>0.1340038399920854</v>
       </c>
     </row>
     <row r="50" spans="1:19">
@@ -3606,34 +3606,34 @@
         <v>31</v>
       </c>
       <c r="E54">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F54">
-        <v>0.02626943535890836</v>
+        <v>0.02355950886601595</v>
       </c>
       <c r="G54">
-        <v>0.04282775839284625</v>
+        <v>0.03468729189248732</v>
       </c>
       <c r="H54">
-        <v>0.1447955471874965</v>
+        <v>0.1421138013729845</v>
       </c>
       <c r="I54">
-        <v>2.012093172129631</v>
+        <v>1.78549636689629</v>
       </c>
       <c r="J54">
-        <v>0.04641277740486038</v>
+        <v>0.07681671444034974</v>
       </c>
       <c r="K54">
-        <v>2569</v>
+        <v>2378</v>
       </c>
       <c r="L54">
-        <v>0.001689584768082849</v>
+        <v>0.00516878245018176</v>
       </c>
       <c r="M54">
-        <v>0.002045039581843465</v>
+        <v>0.006831631268294236</v>
       </c>
       <c r="N54">
-        <v>0.6422764227642277</v>
+        <v>0.6293103448275862</v>
       </c>
       <c r="O54">
         <v>-0.6596764095334604</v>
@@ -3642,10 +3642,10 @@
         <v>-0.05045533964949678</v>
       </c>
       <c r="Q54">
-        <v>0.04282775839284625</v>
+        <v>0.03468729189248732</v>
       </c>
       <c r="R54">
-        <v>0.1103531622747831</v>
+        <v>0.1099107762541712</v>
       </c>
       <c r="S54">
         <v>0.3356838040186936</v>
@@ -4314,46 +4314,46 @@
         <v>31</v>
       </c>
       <c r="E66">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F66">
-        <v>0.01564699893314053</v>
+        <v>0.01310661965420488</v>
       </c>
       <c r="G66">
-        <v>0.03742372199634925</v>
+        <v>0.02996359234545922</v>
       </c>
       <c r="H66">
-        <v>0.1567745419894944</v>
+        <v>0.1545862193588068</v>
       </c>
       <c r="I66">
-        <v>1.106899185808962</v>
+        <v>0.9131642806852884</v>
       </c>
       <c r="J66">
-        <v>0.2705152538330825</v>
+        <v>0.3630666193143772</v>
       </c>
       <c r="K66">
-        <v>2761</v>
+        <v>2552</v>
       </c>
       <c r="L66">
-        <v>0.007922518012299552</v>
+        <v>0.02050630455328767</v>
       </c>
       <c r="M66">
-        <v>0.03004691483554508</v>
+        <v>0.07726226461070651</v>
       </c>
       <c r="N66">
-        <v>0.6016260162601627</v>
+        <v>0.5862068965517241</v>
       </c>
       <c r="O66">
         <v>-0.7990409176250628</v>
       </c>
       <c r="P66">
-        <v>-0.05337295277571576</v>
+        <v>-0.05537844932388805</v>
       </c>
       <c r="Q66">
-        <v>0.03742372199634925</v>
+        <v>0.02996359234545922</v>
       </c>
       <c r="R66">
-        <v>0.1049533610771378</v>
+        <v>0.1038265702088094</v>
       </c>
       <c r="S66">
         <v>0.3199125205821944</v>

--- a/out/final/car_summary.xlsx
+++ b/out/final/car_summary.xlsx
@@ -597,46 +597,46 @@
         <v>28</v>
       </c>
       <c r="E3">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F3">
-        <v>0.011846679371183</v>
+        <v>0.01151580024990956</v>
       </c>
       <c r="G3">
-        <v>0.01826041596976902</v>
+        <v>0.01749065453227544</v>
       </c>
       <c r="H3">
-        <v>0.1042410300849103</v>
+        <v>0.1038817836245635</v>
       </c>
       <c r="I3">
-        <v>1.260406098623651</v>
+        <v>1.234427442498294</v>
       </c>
       <c r="J3">
-        <v>0.2099282749780187</v>
+        <v>0.2193968550434158</v>
       </c>
       <c r="K3">
-        <v>2963</v>
+        <v>3032</v>
       </c>
       <c r="L3">
-        <v>0.03191791631561806</v>
+        <v>0.03553716727833377</v>
       </c>
       <c r="M3">
-        <v>0.01869342540925406</v>
+        <v>0.02437017012239948</v>
       </c>
       <c r="N3">
-        <v>0.6097560975609756</v>
+        <v>0.6048387096774194</v>
       </c>
       <c r="O3">
         <v>-0.6151578735743707</v>
       </c>
       <c r="P3">
-        <v>-0.03654090056664977</v>
+        <v>-0.03648643484885525</v>
       </c>
       <c r="Q3">
-        <v>0.01826041596976902</v>
+        <v>0.01749065453227544</v>
       </c>
       <c r="R3">
-        <v>0.06483036824006777</v>
+        <v>0.06456331767256759</v>
       </c>
       <c r="S3">
         <v>0.2435279385701472</v>
@@ -774,46 +774,46 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="F6">
-        <v>0.01453023091000428</v>
+        <v>0.01959960994508421</v>
       </c>
       <c r="G6">
-        <v>0.02981243299090408</v>
+        <v>0.03087134971765326</v>
       </c>
       <c r="H6">
-        <v>0.1564309012528873</v>
+        <v>0.1527748691228567</v>
       </c>
       <c r="I6">
-        <v>0.9873910591127448</v>
+        <v>1.428585871539553</v>
       </c>
       <c r="J6">
-        <v>0.3255792808740701</v>
+        <v>0.1556577910200216</v>
       </c>
       <c r="K6">
-        <v>2533</v>
+        <v>2874</v>
       </c>
       <c r="L6">
-        <v>0.04888437639545334</v>
+        <v>0.01255362058129347</v>
       </c>
       <c r="M6">
-        <v>0.02353400212601001</v>
+        <v>0.008933408183144214</v>
       </c>
       <c r="N6">
-        <v>0.6106194690265486</v>
+        <v>0.6209677419354839</v>
       </c>
       <c r="O6">
         <v>-0.6596764095334604</v>
       </c>
       <c r="P6">
-        <v>-0.05411590779855757</v>
+        <v>-0.05137048168676198</v>
       </c>
       <c r="Q6">
-        <v>0.02981243299090408</v>
+        <v>0.03087134971765326</v>
       </c>
       <c r="R6">
-        <v>0.1107955482953951</v>
+        <v>0.1116988605193038</v>
       </c>
       <c r="S6">
         <v>0.4111727541048272</v>
@@ -1305,46 +1305,46 @@
         <v>28</v>
       </c>
       <c r="E15">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F15">
-        <v>0.00655069494906158</v>
+        <v>0.006241767964342147</v>
       </c>
       <c r="G15">
-        <v>0.01227505802002051</v>
+        <v>0.01209191355057658</v>
       </c>
       <c r="H15">
-        <v>0.1087255164888246</v>
+        <v>0.1083372713318079</v>
       </c>
       <c r="I15">
-        <v>0.6682030476478505</v>
+        <v>0.6415648613943791</v>
       </c>
       <c r="J15">
-        <v>0.5052662094233906</v>
+        <v>0.5223495153059352</v>
       </c>
       <c r="K15">
-        <v>3146</v>
+        <v>3220</v>
       </c>
       <c r="L15">
-        <v>0.09227116277902724</v>
+        <v>0.1023913118829477</v>
       </c>
       <c r="M15">
-        <v>0.104203866405326</v>
+        <v>0.1265100563218553</v>
       </c>
       <c r="N15">
-        <v>0.5772357723577236</v>
+        <v>0.5725806451612904</v>
       </c>
       <c r="O15">
         <v>-0.7062499396401718</v>
       </c>
       <c r="P15">
-        <v>-0.03982689801495964</v>
+        <v>-0.03964105262416984</v>
       </c>
       <c r="Q15">
-        <v>0.01227505802002051</v>
+        <v>0.01209191355057658</v>
       </c>
       <c r="R15">
-        <v>0.06078985363324877</v>
+        <v>0.05972039529923064</v>
       </c>
       <c r="S15">
         <v>0.23121546078401</v>
@@ -1482,46 +1482,46 @@
         <v>31</v>
       </c>
       <c r="E18">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="F18">
-        <v>0.003138137240721788</v>
+        <v>0.008421452318361796</v>
       </c>
       <c r="G18">
-        <v>0.01964699738379661</v>
+        <v>0.02411083778016018</v>
       </c>
       <c r="H18">
-        <v>0.1685281231336839</v>
+        <v>0.1640435629136172</v>
       </c>
       <c r="I18">
-        <v>0.1979423720442414</v>
+        <v>0.5716611035342841</v>
       </c>
       <c r="J18">
-        <v>0.8434489746478218</v>
+        <v>0.5685947870115527</v>
       </c>
       <c r="K18">
-        <v>2705</v>
+        <v>3096</v>
       </c>
       <c r="L18">
-        <v>0.1397182781603141</v>
+        <v>0.05206601610488708</v>
       </c>
       <c r="M18">
-        <v>0.1319242908242605</v>
+        <v>0.0588758732807349</v>
       </c>
       <c r="N18">
-        <v>0.5752212389380531</v>
+        <v>0.5887096774193549</v>
       </c>
       <c r="O18">
         <v>-0.7990409176250628</v>
       </c>
       <c r="P18">
-        <v>-0.06139493896840495</v>
+        <v>-0.0597494993096539</v>
       </c>
       <c r="Q18">
-        <v>0.01964699738379661</v>
+        <v>0.02411083778016018</v>
       </c>
       <c r="R18">
-        <v>0.101516322217895</v>
+        <v>0.101684976887558</v>
       </c>
       <c r="S18">
         <v>0.3881814630189198</v>
@@ -2013,46 +2013,46 @@
         <v>28</v>
       </c>
       <c r="E27">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F27">
-        <v>0.006708564240445972</v>
+        <v>0.006219639417183161</v>
       </c>
       <c r="G27">
-        <v>0.02280284036827662</v>
+        <v>0.02237031572496173</v>
       </c>
       <c r="H27">
-        <v>0.1116811888899429</v>
+        <v>0.1113594444699247</v>
       </c>
       <c r="I27">
-        <v>0.6661961370018944</v>
+        <v>0.6219407228813506</v>
       </c>
       <c r="J27">
-        <v>0.5065435270797732</v>
+        <v>0.535131982092142</v>
       </c>
       <c r="K27">
-        <v>3172</v>
+        <v>3254</v>
       </c>
       <c r="L27">
-        <v>0.1056830976755944</v>
+        <v>0.121483373908952</v>
       </c>
       <c r="M27">
-        <v>0.07090166737501427</v>
+        <v>0.08755276689017025</v>
       </c>
       <c r="N27">
-        <v>0.5853658536585366</v>
+        <v>0.5806451612903226</v>
       </c>
       <c r="O27">
         <v>-0.6151578735743707</v>
       </c>
       <c r="P27">
-        <v>-0.04283554106527321</v>
+        <v>-0.04339235866239588</v>
       </c>
       <c r="Q27">
-        <v>0.02280284036827662</v>
+        <v>0.02237031572496173</v>
       </c>
       <c r="R27">
-        <v>0.07188164379608386</v>
+        <v>0.0712216236174707</v>
       </c>
       <c r="S27">
         <v>0.3051966849554455</v>
@@ -2190,46 +2190,46 @@
         <v>31</v>
       </c>
       <c r="E30">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F30">
-        <v>0.02157332801105191</v>
+        <v>0.02068685738557012</v>
       </c>
       <c r="G30">
-        <v>0.02875506432362873</v>
+        <v>0.04164348503928761</v>
       </c>
       <c r="H30">
-        <v>0.1316295173107571</v>
+        <v>0.1333996785033894</v>
       </c>
       <c r="I30">
-        <v>1.772787941080474</v>
+        <v>1.726833956760966</v>
       </c>
       <c r="J30">
-        <v>0.07888867379461235</v>
+        <v>0.08670798007031066</v>
       </c>
       <c r="K30">
-        <v>2571</v>
+        <v>2884</v>
       </c>
       <c r="L30">
-        <v>0.01662961545289519</v>
+        <v>0.01346454013877876</v>
       </c>
       <c r="M30">
-        <v>0.01586449682440639</v>
+        <v>0.008933408183144214</v>
       </c>
       <c r="N30">
-        <v>0.6153846153846154</v>
+        <v>0.6209677419354839</v>
       </c>
       <c r="O30">
         <v>-0.6008766263938626</v>
       </c>
       <c r="P30">
-        <v>-0.04092888223349755</v>
+        <v>-0.04336012400587688</v>
       </c>
       <c r="Q30">
-        <v>0.02875506432362873</v>
+        <v>0.04164348503928761</v>
       </c>
       <c r="R30">
-        <v>0.1084904019670709</v>
+        <v>0.1079721845222246</v>
       </c>
       <c r="S30">
         <v>0.3268837448716404</v>
@@ -2721,46 +2721,46 @@
         <v>28</v>
       </c>
       <c r="E39">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F39">
-        <v>0.001031925172357973</v>
+        <v>0.0005618568134627335</v>
       </c>
       <c r="G39">
-        <v>0.01949474818299934</v>
+        <v>0.01937859153722251</v>
       </c>
       <c r="H39">
-        <v>0.1172557310484154</v>
+        <v>0.1168953647705651</v>
       </c>
       <c r="I39">
-        <v>0.09760379039548521</v>
+        <v>0.05352284667832721</v>
       </c>
       <c r="J39">
-        <v>0.922407085391908</v>
+        <v>0.9574021612670761</v>
       </c>
       <c r="K39">
-        <v>3339</v>
+        <v>3425</v>
       </c>
       <c r="L39">
-        <v>0.231543839121331</v>
+        <v>0.2617955045151033</v>
       </c>
       <c r="M39">
-        <v>0.07090166737501427</v>
+        <v>0.08755276689017025</v>
       </c>
       <c r="N39">
-        <v>0.5853658536585366</v>
+        <v>0.5806451612903226</v>
       </c>
       <c r="O39">
         <v>-0.7062499396401718</v>
       </c>
       <c r="P39">
-        <v>-0.04812958569048796</v>
+        <v>-0.04911711444563376</v>
       </c>
       <c r="Q39">
-        <v>0.01949474818299934</v>
+        <v>0.01937859153722251</v>
       </c>
       <c r="R39">
-        <v>0.06851782290002735</v>
+        <v>0.06776704247396076</v>
       </c>
       <c r="S39">
         <v>0.2928243202433803</v>
@@ -2898,46 +2898,46 @@
         <v>31</v>
       </c>
       <c r="E42">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F42">
-        <v>0.01134672521257036</v>
+        <v>0.01026876264575137</v>
       </c>
       <c r="G42">
-        <v>0.02248817084313751</v>
+        <v>0.03132514247101227</v>
       </c>
       <c r="H42">
-        <v>0.1404098832904531</v>
+        <v>0.1419998104779066</v>
       </c>
       <c r="I42">
-        <v>0.8741093989351132</v>
+        <v>0.8052693946133146</v>
       </c>
       <c r="J42">
-        <v>0.3838647670930379</v>
+        <v>0.4222181763986949</v>
       </c>
       <c r="K42">
-        <v>2830</v>
+        <v>3171</v>
       </c>
       <c r="L42">
-        <v>0.09095829414910434</v>
+        <v>0.07916476785880125</v>
       </c>
       <c r="M42">
-        <v>0.06399591064679504</v>
+        <v>0.03844849701100047</v>
       </c>
       <c r="N42">
-        <v>0.5897435897435898</v>
+        <v>0.5967741935483871</v>
       </c>
       <c r="O42">
         <v>-0.758055079046148</v>
       </c>
       <c r="P42">
-        <v>-0.04740580174051361</v>
+        <v>-0.04908803055779336</v>
       </c>
       <c r="Q42">
-        <v>0.02248817084313751</v>
+        <v>0.03132514247101227</v>
       </c>
       <c r="R42">
-        <v>0.09787977436595499</v>
+        <v>0.09708808206814362</v>
       </c>
       <c r="S42">
         <v>0.3182231058569503</v>
@@ -3606,34 +3606,34 @@
         <v>31</v>
       </c>
       <c r="E54">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F54">
-        <v>0.02355950886601595</v>
+        <v>0.02626943535890836</v>
       </c>
       <c r="G54">
-        <v>0.03468729189248732</v>
+        <v>0.04282775839284625</v>
       </c>
       <c r="H54">
-        <v>0.1421138013729845</v>
+        <v>0.1447955471874965</v>
       </c>
       <c r="I54">
-        <v>1.78549636689629</v>
+        <v>2.012093172129631</v>
       </c>
       <c r="J54">
-        <v>0.07681671444034974</v>
+        <v>0.04641277740486038</v>
       </c>
       <c r="K54">
-        <v>2378</v>
+        <v>2569</v>
       </c>
       <c r="L54">
-        <v>0.00516878245018176</v>
+        <v>0.001689584768082849</v>
       </c>
       <c r="M54">
-        <v>0.006831631268294236</v>
+        <v>0.002045039581843465</v>
       </c>
       <c r="N54">
-        <v>0.6293103448275862</v>
+        <v>0.6422764227642277</v>
       </c>
       <c r="O54">
         <v>-0.6596764095334604</v>
@@ -3642,10 +3642,10 @@
         <v>-0.05045533964949678</v>
       </c>
       <c r="Q54">
-        <v>0.03468729189248732</v>
+        <v>0.04282775839284625</v>
       </c>
       <c r="R54">
-        <v>0.1099107762541712</v>
+        <v>0.1103531622747831</v>
       </c>
       <c r="S54">
         <v>0.3356838040186936</v>
@@ -4314,46 +4314,46 @@
         <v>31</v>
       </c>
       <c r="E66">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F66">
-        <v>0.01310661965420488</v>
+        <v>0.01564699893314053</v>
       </c>
       <c r="G66">
-        <v>0.02996359234545922</v>
+        <v>0.03742372199634925</v>
       </c>
       <c r="H66">
-        <v>0.1545862193588068</v>
+        <v>0.1567745419894944</v>
       </c>
       <c r="I66">
-        <v>0.9131642806852884</v>
+        <v>1.106899185808962</v>
       </c>
       <c r="J66">
-        <v>0.3630666193143772</v>
+        <v>0.2705152538330825</v>
       </c>
       <c r="K66">
-        <v>2552</v>
+        <v>2761</v>
       </c>
       <c r="L66">
-        <v>0.02050630455328767</v>
+        <v>0.007922518012299552</v>
       </c>
       <c r="M66">
-        <v>0.07726226461070651</v>
+        <v>0.03004691483554508</v>
       </c>
       <c r="N66">
-        <v>0.5862068965517241</v>
+        <v>0.6016260162601627</v>
       </c>
       <c r="O66">
         <v>-0.7990409176250628</v>
       </c>
       <c r="P66">
-        <v>-0.05537844932388805</v>
+        <v>-0.05337295277571576</v>
       </c>
       <c r="Q66">
-        <v>0.02996359234545922</v>
+        <v>0.03742372199634925</v>
       </c>
       <c r="R66">
-        <v>0.1038265702088094</v>
+        <v>0.1049533610771378</v>
       </c>
       <c r="S66">
         <v>0.3199125205821944</v>
